--- a/artfynd/A 575-2024 artfynd.xlsx
+++ b/artfynd/A 575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118836350</v>
+        <v>118832909</v>
       </c>
       <c r="B2" t="n">
-        <v>57659</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533261</v>
+        <v>533253</v>
       </c>
       <c r="R2" t="n">
-        <v>6547816</v>
+        <v>6547825</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118832909</v>
+        <v>118833402</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>57718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533253</v>
+        <v>533301</v>
       </c>
       <c r="R3" t="n">
         <v>6547825</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118833402</v>
+        <v>118836350</v>
       </c>
       <c r="B4" t="n">
-        <v>57718</v>
+        <v>57659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533301</v>
+        <v>533261</v>
       </c>
       <c r="R4" t="n">
-        <v>6547825</v>
+        <v>6547816</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1019,22 +1019,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 575-2024 artfynd.xlsx
+++ b/artfynd/A 575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118832909</v>
+        <v>118833402</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533253</v>
+        <v>533301</v>
       </c>
       <c r="R2" t="n">
         <v>6547825</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118833402</v>
+        <v>118832909</v>
       </c>
       <c r="B3" t="n">
-        <v>57718</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533301</v>
+        <v>533253</v>
       </c>
       <c r="R3" t="n">
         <v>6547825</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 575-2024 artfynd.xlsx
+++ b/artfynd/A 575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118833402</v>
+        <v>118836350</v>
       </c>
       <c r="B2" t="n">
-        <v>57718</v>
+        <v>57659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533301</v>
+        <v>533261</v>
       </c>
       <c r="R2" t="n">
-        <v>6547825</v>
+        <v>6547816</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118836350</v>
+        <v>118833402</v>
       </c>
       <c r="B4" t="n">
-        <v>57659</v>
+        <v>57718</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533261</v>
+        <v>533301</v>
       </c>
       <c r="R4" t="n">
-        <v>6547816</v>
+        <v>6547825</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1019,22 +1019,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 575-2024 artfynd.xlsx
+++ b/artfynd/A 575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118836350</v>
+        <v>118833402</v>
       </c>
       <c r="B2" t="n">
-        <v>57659</v>
+        <v>57718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533261</v>
+        <v>533301</v>
       </c>
       <c r="R2" t="n">
-        <v>6547816</v>
+        <v>6547825</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118833402</v>
+        <v>118836350</v>
       </c>
       <c r="B4" t="n">
-        <v>57718</v>
+        <v>57659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533301</v>
+        <v>533261</v>
       </c>
       <c r="R4" t="n">
-        <v>6547825</v>
+        <v>6547816</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1019,22 +1019,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 575-2024 artfynd.xlsx
+++ b/artfynd/A 575-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118832909</v>
+        <v>118833402</v>
       </c>
       <c r="B2" t="n">
-        <v>57539</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533253</v>
+        <v>533301</v>
       </c>
       <c r="R2" t="n">
         <v>6547825</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,37 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118836350</v>
+        <v>118832909</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533261</v>
+        <v>533253</v>
       </c>
       <c r="R3" t="n">
-        <v>6547816</v>
+        <v>6547825</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,37 +925,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118833402</v>
+        <v>118836350</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533301</v>
+        <v>533261</v>
       </c>
       <c r="R4" t="n">
-        <v>6547825</v>
+        <v>6547816</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1019,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 575-2024 artfynd.xlsx
+++ b/artfynd/A 575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118833402</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118832909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,8 +1062,18 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118836350</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>